--- a/artfynd/A 55989-2023 artfynd.xlsx
+++ b/artfynd/A 55989-2023 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115638579</v>
+        <v>115638628</v>
       </c>
       <c r="B2" t="n">
-        <v>56183</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>100015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -766,6 +761,11 @@
           <t>2023-09-03</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Granskad av Alexander Eriksson samt Johan Eklöf</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -798,12 +798,7 @@
         <v>115638590</v>
       </c>
       <c r="B3" t="n">
-        <v>56178</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,42 +910,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115638572</v>
+        <v>115638613</v>
       </c>
       <c r="B4" t="n">
-        <v>56185</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1035,15 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115638613</v>
+        <v>115638579</v>
       </c>
       <c r="B5" t="n">
-        <v>56171</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1158,12 +1143,7 @@
         <v>115638638</v>
       </c>
       <c r="B6" t="n">
-        <v>56164</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,15 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115638628</v>
+        <v>115638572</v>
       </c>
       <c r="B7" t="n">
-        <v>56174</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,26 +1266,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100015</v>
+        <v>206002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1364,11 +1339,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Granskad av Alexander Eriksson samt Johan Eklöf</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 55989-2023 artfynd.xlsx
+++ b/artfynd/A 55989-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115638628</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115638590</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115638613</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115638579</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115638638</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,8 +1397,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115638572</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>